--- a/Predictions/2026-04-11.xlsx
+++ b/Predictions/2026-04-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B7F3A9-7CC8-4AC9-9D03-A45FE01D6FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC619D4-7546-4848-9AAA-47B25389A4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
   <si>
     <t>Red Corner</t>
   </si>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>Glicko-2</t>
-  </si>
-  <si>
-    <t>GDScore</t>
   </si>
   <si>
     <t>Win%</t>
@@ -206,7 +203,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,12 +228,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -339,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -401,18 +392,6 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -425,7 +404,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -733,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -750,34 +732,28 @@
     <col min="12" max="12" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D1" s="25" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D1" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="27"/>
-      <c r="M1" s="25" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="23"/>
+      <c r="M1" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="27"/>
-      <c r="O1" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="27"/>
+      <c r="N1" s="23"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +788,7 @@
         <v>44</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>3</v>
@@ -820,14 +796,8 @@
       <c r="N2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -837,25 +807,25 @@
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>0.60535905718763705</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="25">
         <v>0.91331006484749533</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="25">
         <v>6.5410080607720245E-2</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="25">
         <v>0.91331006484749533</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="27">
         <v>2.1279854544784541E-2</v>
       </c>
       <c r="K3" s="14" t="s">
@@ -870,14 +840,8 @@
       <c r="N3" s="15">
         <v>0.50018507268062584</v>
       </c>
-      <c r="O3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="15">
-        <v>0.5078445238842304</v>
-      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -887,47 +851,41 @@
       <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>0.65510896174429289</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="25">
         <v>0.65611903504581492</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="25">
         <v>0.65611903504581492</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="25">
         <v>0.28125040417498581</v>
       </c>
-      <c r="J4" s="24">
+      <c r="J4" s="27">
         <v>6.2630560779199332E-2</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="13">
         <v>0.61390594850624325</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="9">
         <v>0.6157901753840741</v>
       </c>
-      <c r="O4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="15">
-        <v>0.5228364300334305</v>
-      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -970,14 +928,8 @@
       <c r="N5" s="9">
         <v>0.66100280855069304</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0.50493519267017495</v>
-      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -1020,14 +972,8 @@
       <c r="N6" s="15">
         <v>0.55158940026833769</v>
       </c>
-      <c r="O6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="15">
-        <v>0.50184823340319473</v>
-      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1070,14 +1016,8 @@
       <c r="N7" s="15">
         <v>0.66604265799876528</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0.51601624969032345</v>
-      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1120,14 +1060,8 @@
       <c r="N8" s="9">
         <v>0.62905127886873013</v>
       </c>
-      <c r="O8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="15">
-        <v>0.56559968957340212</v>
-      </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -1170,14 +1104,8 @@
       <c r="N9" s="9">
         <v>0.56324307386373107</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0.50273057418014222</v>
-      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -1220,14 +1148,8 @@
       <c r="N10" s="15">
         <v>0.64797586268682217</v>
       </c>
-      <c r="O10" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" s="15">
-        <v>0.63962758425516308</v>
-      </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -1270,14 +1192,8 @@
       <c r="N11" s="15">
         <v>0.72406822281849748</v>
       </c>
-      <c r="O11" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="15">
-        <v>0.54748505940456138</v>
-      </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1320,14 +1236,8 @@
       <c r="N12" s="15">
         <v>0.57960859379381358</v>
       </c>
-      <c r="O12" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="P12" s="15">
-        <v>0.57733230169657379</v>
-      </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -1370,14 +1280,8 @@
       <c r="N13" s="15">
         <v>0.52789942603261997</v>
       </c>
-      <c r="O13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0.51502119403122681</v>
-      </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -1420,18 +1324,11 @@
       <c r="N14" s="15">
         <v>0.68006058395396218</v>
       </c>
-      <c r="O14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="P14" s="15">
-        <v>0.55792241556839794</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Predictions/2026-04-11.xlsx
+++ b/Predictions/2026-04-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC619D4-7546-4848-9AAA-47B25389A4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64A9DCE-A434-4260-A6BD-B597B6550304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
   <si>
     <t>Red Corner</t>
   </si>
@@ -158,12 +158,6 @@
   </si>
   <si>
     <t>Glicko-2</t>
-  </si>
-  <si>
-    <t>Win%</t>
-  </si>
-  <si>
-    <t>Old Model</t>
   </si>
 </sst>
 </file>
@@ -330,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -347,9 +341,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -368,9 +359,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -381,9 +369,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -400,18 +385,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -715,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -729,31 +702,25 @@
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="21" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D1" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="21" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="23"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L1" s="20"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,13 +730,13 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -781,23 +748,17 @@
       <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -807,41 +768,35 @@
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="3">
         <v>0.60535905718763705</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="3">
         <v>0.91331006484749533</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="3">
         <v>6.5410080607720245E-2</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="3">
         <v>0.91331006484749533</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="8">
         <v>2.1279854544784541E-2</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="18">
-        <v>0.60043346794262753</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="15">
+      <c r="L3" s="13">
         <v>0.50018507268062584</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -851,41 +806,35 @@
       <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="3">
         <v>0.65510896174429289</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="3">
         <v>0.65611903504581492</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="3">
         <v>0.65611903504581492</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="3">
         <v>0.28125040417498581</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="8">
         <v>6.2630560779199332E-2</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="13">
-        <v>0.61390594850624325</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="9">
+      <c r="L4" s="8">
         <v>0.6157901753840741</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -895,10 +844,10 @@
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <v>0.61872922116539686</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -907,29 +856,23 @@
       <c r="G5" s="3">
         <v>0.55769120176708731</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="17">
         <v>0.13097250908281269</v>
       </c>
       <c r="I5" s="3">
         <v>0.55769120176708731</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0.31133628915010009</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="18">
-        <v>0.54590699962642231</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="9">
+      <c r="L5" s="8">
         <v>0.66100280855069304</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -939,10 +882,10 @@
       <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <v>0.50078905405388963</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -951,29 +894,23 @@
       <c r="G6" s="3">
         <v>0.72646991844720465</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="17">
         <v>0.25263646349816449</v>
       </c>
       <c r="I6" s="3">
         <v>0.72646991844720465</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>2.0893618054630868E-2</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="18">
-        <v>0.62909497265117198</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="15">
+      <c r="L6" s="13">
         <v>0.55158940026833769</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -983,10 +920,10 @@
       <c r="C7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="14">
         <v>0.65542641407314295</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -998,26 +935,20 @@
       <c r="H7" s="3">
         <v>0.50247128731254265</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="17">
         <v>0.40692688043045078</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>9.0601832257006576E-2</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="18">
-        <v>0.55659596675103706</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="L7" s="13">
         <v>0.66604265799876528</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1027,41 +958,35 @@
       <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <v>0.65406413481384607</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="14">
         <v>0.66307489594743385</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="14">
         <v>0.66307489594743385</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="14">
         <v>0.19116688040125149</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="13">
         <v>0.14575822365131469</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="18">
-        <v>0.57179149169361243</v>
-      </c>
-      <c r="M8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="9">
+      <c r="L8" s="8">
         <v>0.62905127886873013</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -1071,10 +996,10 @@
       <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="14">
         <v>0.62837542784580158</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -1083,29 +1008,23 @@
       <c r="G9" s="3">
         <v>0.51853499736192332</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="17">
         <v>0.25266331756152088</v>
       </c>
       <c r="I9" s="3">
         <v>0.51853499736192332</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0.22880168507655571</v>
       </c>
-      <c r="K9" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="18">
-        <v>0.55270285008584064</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N9" s="9">
+      <c r="L9" s="8">
         <v>0.56324307386373107</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -1115,10 +1034,10 @@
       <c r="C10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="14">
         <v>0.69875361118503843</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1133,23 +1052,17 @@
       <c r="I10" s="3">
         <v>0.1477199239517131</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="16">
         <v>0.28308730042838542</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="18">
-        <v>0.56490283014993981</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="15">
+      <c r="L10" s="13">
         <v>0.64797586268682217</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -1159,10 +1072,10 @@
       <c r="C11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="14">
         <v>0.74581382508750549</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1177,23 +1090,17 @@
       <c r="I11" s="3">
         <v>7.0263911443279287E-2</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="16">
         <v>7.991350548308368E-2</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="18">
-        <v>0.536960210509005</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="15">
+      <c r="L11" s="13">
         <v>0.72406822281849748</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1203,41 +1110,35 @@
       <c r="C12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="14">
         <v>0.54722990303410646</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="14">
         <v>0.50406387355942539</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="14">
         <v>0.50406387355942539</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="14">
         <v>0.45035525644276042</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="13">
         <v>4.5580869997814299E-2</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="18">
-        <v>0.53571304210722315</v>
-      </c>
-      <c r="M12" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="15">
+      <c r="L12" s="13">
         <v>0.57960859379381358</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -1247,10 +1148,10 @@
       <c r="C13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="14">
         <v>0.54612978211126118</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1265,23 +1166,17 @@
       <c r="I13" s="3">
         <v>0.56247369897983779</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="16">
         <v>0.1563520334674488</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="18">
-        <v>0.58135312666807704</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="N13" s="15">
+      <c r="L13" s="13">
         <v>0.52789942603261997</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -1291,44 +1186,37 @@
       <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="14">
         <v>0.69588198861703976</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="14">
         <v>0.67778613261633702</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="14">
         <v>0.67778613261633702</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="14">
         <v>5.9315591844774529E-2</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="13">
         <v>0.26289827553888839</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>41</v>
+      <c r="K14" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="L14" s="13">
-        <v>0.5502272871970304</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="N14" s="15">
         <v>0.68006058395396218</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="D1:J1"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
